--- a/artfynd/A 36434-2026 artfynd.xlsx
+++ b/artfynd/A 36434-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73700579</v>
+        <v>137386042</v>
       </c>
       <c r="B3" t="n">
-        <v>57767</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,41 +801,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205497</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ägretthäger</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ardea alba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hållsdammen, Gläntan, Vg</t>
+          <t>Dicksonsdammen öster om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453818</v>
+        <v>453781</v>
       </c>
       <c r="R3" t="n">
-        <v>6458327</v>
+        <v>6458351</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,73 +871,74 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Aastrup</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Aastrup</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73700579</t>
+          <t>https://artportalen.se/Sighting/137386042</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>83340578</v>
+        <v>137386054</v>
       </c>
       <c r="B4" t="n">
-        <v>106813</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>VGL Träd ID: 18832, Vg</t>
+          <t>Dicksonsdammen öster om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454002</v>
+        <v>453759</v>
       </c>
       <c r="R4" t="n">
-        <v>6458430</v>
+        <v>6458527</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,19 +960,14 @@
           <t>Norra Fågelås</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4F8CE004-9FA4-43D6-BC09-49816490ADE8</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-07-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-07-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,24 +978,900 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137386054</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137386061</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93463</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dicksonsdammen öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>453730</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6458582</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137386061</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137386055</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93475</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dicksonsdammen öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>453730</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6458527</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137386055</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137386062</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93475</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dicksonsdammen öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>453730</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6458582</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137386062</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137386063</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93501</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dicksonsdammen öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>453730</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6458582</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137386063</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73700579</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57767</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205497</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ägretthäger</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ardea alba</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hållsdammen, Gläntan, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>453818</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6458327</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-10-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-10-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Peter Aastrup</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Peter Aastrup</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73700579</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137386053</v>
+      </c>
+      <c r="B10" t="n">
+        <v>111407</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dicksonsdammen öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>453759</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6458527</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137386053</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137386064</v>
+      </c>
+      <c r="B11" t="n">
+        <v>111407</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dicksonsdammen öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>453796</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6458366</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrskog och barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137386064</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>83340578</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>VGL Träd ID: 18832, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>454002</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6458430</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hjo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Fågelås</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4F8CE004-9FA4-43D6-BC09-49816490ADE8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2007-07-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2007-07-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Lars Sjögren</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Lars Sjögren, Jan Mastera</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/83340578</t>
         </is>
@@ -1024,6 +1882,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36434-2026 artfynd.xlsx
+++ b/artfynd/A 36434-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386042</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386054</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137386061</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>137386055</v>
       </c>
       <c r="B6" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>137386062</v>
       </c>
       <c r="B7" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>137386063</v>
       </c>
       <c r="B8" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>137386053</v>
       </c>
       <c r="B10" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>137386064</v>
       </c>
       <c r="B11" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36434-2026 artfynd.xlsx
+++ b/artfynd/A 36434-2026 artfynd.xlsx
@@ -1553,7 +1553,7 @@
         <v>137386053</v>
       </c>
       <c r="B10" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>137386064</v>
       </c>
       <c r="B11" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36434-2026 artfynd.xlsx
+++ b/artfynd/A 36434-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386042</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386054</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137386061</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>137386055</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>137386062</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>137386063</v>
       </c>
       <c r="B8" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>137386053</v>
       </c>
       <c r="B10" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>137386064</v>
       </c>
       <c r="B11" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36434-2026 artfynd.xlsx
+++ b/artfynd/A 36434-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386042</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386054</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137386061</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>137386055</v>
       </c>
       <c r="B6" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>137386062</v>
       </c>
       <c r="B7" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>137386063</v>
       </c>
       <c r="B8" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>137386053</v>
       </c>
       <c r="B10" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>137386064</v>
       </c>
       <c r="B11" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36434-2026 artfynd.xlsx
+++ b/artfynd/A 36434-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386042</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386054</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137386061</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>137386055</v>
       </c>
       <c r="B6" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>137386062</v>
       </c>
       <c r="B7" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>137386063</v>
       </c>
       <c r="B8" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>137386053</v>
       </c>
       <c r="B10" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>137386064</v>
       </c>
       <c r="B11" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36434-2026 artfynd.xlsx
+++ b/artfynd/A 36434-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137386042</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137386054</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137386061</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>137386055</v>
       </c>
       <c r="B6" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>137386062</v>
       </c>
       <c r="B7" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>137386063</v>
       </c>
       <c r="B8" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>137386053</v>
       </c>
       <c r="B10" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>137386064</v>
       </c>
       <c r="B11" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
